--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Consigli e Giunte comunali.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Consigli e Giunte comunali.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="106">
   <si>
     <r>
       <t xml:space="preserve">
@@ -160,7 +160,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Vedi delibere</t>
+    <t>Vai alle delibere</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -362,7 +362,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>Streaming della seduta del Consiglio comunale</t>
+      <t>Diretta streaming della seduta del Consiglio comunale</t>
     </r>
   </si>
   <si>
@@ -821,7 +821,7 @@
       </rPr>
       <t xml:space="preserve"> si svolgeranno le seguenti sedute del Consiglio comunale:
 [Inserire qui elenco delle date nel seguente modo:
--  </t>
+- </t>
     </r>
     <r>
       <rPr>
@@ -873,7 +873,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
--  </t>
+- </t>
     </r>
     <r>
       <rPr>
@@ -1468,7 +1468,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1545,9 +1545,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
   </si>
 </sst>
 </file>
@@ -2411,7 +2408,7 @@
         <v>105</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>58</v>
@@ -2426,7 +2423,7 @@
         <v>58</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>58</v>
